--- a/vibration_data/stud_FDU_z-direction_CloseChamber_100gain_best_spring.xlsx
+++ b/vibration_data/stud_FDU_z-direction_CloseChamber_100gain_best_spring.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="16" uniqueCount="8">
   <si>
     <t>Material</t>
   </si>
@@ -85,13 +85,13 @@
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.3046875" customWidth="true"/>
-    <col min="2" max="2" width="18.3828125" customWidth="true"/>
-    <col min="3" max="3" width="19.15234375" customWidth="true"/>
-    <col min="4" max="4" width="13.69140625" customWidth="true"/>
-    <col min="5" max="5" width="17.15234375" customWidth="true"/>
-    <col min="6" max="6" width="13.765625" customWidth="true"/>
-    <col min="7" max="7" width="24.84375" customWidth="true"/>
+    <col min="1" max="1" width="8.5703125" customWidth="true"/>
+    <col min="2" max="2" width="19.42578125" customWidth="true"/>
+    <col min="3" max="3" width="20.140625" customWidth="true"/>
+    <col min="4" max="4" width="14.28515625" customWidth="true"/>
+    <col min="5" max="5" width="18.140625" customWidth="true"/>
+    <col min="6" max="6" width="14.7109375" customWidth="true"/>
+    <col min="7" max="7" width="26.5703125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/vibration_data/stud_FDU_z-direction_CloseChamber_100gain_best_spring.xlsx
+++ b/vibration_data/stud_FDU_z-direction_CloseChamber_100gain_best_spring.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="16" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="32" uniqueCount="8">
   <si>
     <t>Material</t>
   </si>
